--- a/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260806.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260806.xlsx
@@ -1173,17 +1173,17 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>2458</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>大成</t>
+          <t>義隆</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>21,432,000</t>
+          <t>8,032,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1195,17 +1195,17 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>義隆</t>
+          <t>大成</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>8,032,000</t>
+          <t>21,432,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1349,17 +1349,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>儒鴻</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>2,967,000</t>
+          <t>16,660,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1371,17 +1371,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>聚陽</t>
+          <t>儒鴻</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>4,769,000</t>
+          <t>2,967,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>聚陽</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>2,115,678</t>
+          <t>4,769,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>16,660,000</t>
+          <t>2,115,678</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
